--- a/tabtools/demo/tablex.xlsx
+++ b/tabtools/demo/tablex.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="30" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="90" uniqueCount="18">
   <si>
     <t>Table 4. Summary by Origin</t>
   </si>
@@ -73,10 +73,974 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="114">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="340">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -569,7 +1533,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="80">
+  <borders count="238">
     <border>
       <left/>
       <right/>
@@ -1106,11 +2070,1069 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="238">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -1413,6 +3435,614 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="81" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" xfId="0"/>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="181" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="183" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="185" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="186" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="187" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="188" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="189" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="190" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="191" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="192" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="193" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="194" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="195" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="196" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="197" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="198" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="199" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="200" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="201" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="202" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="204" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="206" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="208" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="210" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="212" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="214" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="216" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="218" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="220" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="222" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="224" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="226" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="159" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="160" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="161" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="162" xfId="0"/>
+    <xf numFmtId="0" fontId="227" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="228" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="229" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="230" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="231" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="232" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="233" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="234" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="235" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="236" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="238" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="240" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="242" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="244" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="246" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="248" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="250" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="252" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="254" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="256" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="257" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="258" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="259" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="260" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="261" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="263" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="265" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="267" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="269" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="271" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="273" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="275" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="277" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="279" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="281" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="283" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="285" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="287" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="289" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="291" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="293" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="294" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="295" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="296" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="297" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="298" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="299" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="300" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="301" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="302" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="303" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="304" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="305" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="306" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="307" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="308" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="309" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="310" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="311" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="312" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="313" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="314" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="315" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="317" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="319" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="321" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="323" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="325" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="327" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="329" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="331" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="333" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="335" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="337" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="339" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1428,110 +4058,110 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="2" customWidth="true"/>
-    <col min="2" max="2" width="12.7109375" style="3" customWidth="true"/>
-    <col min="3" max="5" width="15.7109375" style="4" customWidth="true"/>
+    <col min="1" max="1" width="2.7109375" style="160" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" style="161" customWidth="true"/>
+    <col min="3" max="5" width="15.7109375" style="162" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="25" t="s">
+    <row r="1" s="159" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="183" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="183" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="183" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="183" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="183" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="212" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="205" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="206" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="217" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="213" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="209" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="210" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="60" t="s">
+      <c r="E3" s="218" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="226" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="69" t="s">
+      <c r="C4" s="227" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="70" t="s">
+      <c r="D4" s="228" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="71" t="s">
+      <c r="E4" s="229" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="72" t="s">
+      <c r="B5" s="230" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="73" t="s">
+      <c r="C5" s="231" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="74" t="s">
+      <c r="D5" s="232" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="75" t="s">
+      <c r="E5" s="233" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="76" t="s">
+      <c r="B6" s="234" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="77" t="s">
+      <c r="C6" s="235" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="236" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="79" t="s">
+      <c r="E6" s="237" t="s">
         <v>17</v>
       </c>
     </row>

--- a/tabtools/demo/tablex.xlsx
+++ b/tabtools/demo/tablex.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="90" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="120" uniqueCount="18">
   <si>
     <t>Table 4. Summary by Origin</t>
   </si>
@@ -73,10 +73,492 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="340">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="453">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1533,7 +2015,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="238">
+  <borders count="317">
     <border>
       <left/>
       <right/>
@@ -3128,11 +3610,540 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="238">
+  <cellXfs count="317">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -4043,6 +5054,310 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="339" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="238" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="239" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="240" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="241" xfId="0"/>
+    <xf numFmtId="0" fontId="340" fillId="0" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="341" fillId="0" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="342" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="343" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="344" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="345" fillId="0" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="346" fillId="0" borderId="248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="347" fillId="0" borderId="249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="348" fillId="0" borderId="250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="349" fillId="0" borderId="251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="351" fillId="0" borderId="252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="353" fillId="0" borderId="253" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="355" fillId="0" borderId="254" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="357" fillId="0" borderId="255" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="359" fillId="0" borderId="256" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="361" fillId="0" borderId="257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="363" fillId="0" borderId="258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="365" fillId="0" borderId="259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="367" fillId="0" borderId="260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="369" fillId="0" borderId="261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="370" fillId="0" borderId="262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="371" fillId="0" borderId="263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="372" fillId="0" borderId="264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="373" fillId="0" borderId="265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="374" fillId="0" borderId="266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="376" fillId="0" borderId="267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="378" fillId="0" borderId="268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="380" fillId="0" borderId="269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="382" fillId="0" borderId="270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="384" fillId="0" borderId="271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="386" fillId="0" borderId="272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="388" fillId="0" borderId="273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="390" fillId="0" borderId="274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="392" fillId="0" borderId="275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="394" fillId="0" borderId="276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="396" fillId="0" borderId="277" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="398" fillId="0" borderId="278" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="400" fillId="0" borderId="279" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="402" fillId="0" borderId="280" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="404" fillId="0" borderId="281" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="406" fillId="0" borderId="282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="407" fillId="0" borderId="283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="408" fillId="0" borderId="284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="409" fillId="0" borderId="285" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="410" fillId="0" borderId="286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="411" fillId="0" borderId="287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="412" fillId="0" borderId="288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="413" fillId="0" borderId="289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="414" fillId="0" borderId="290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="415" fillId="0" borderId="291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="416" fillId="0" borderId="292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="417" fillId="0" borderId="293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="418" fillId="0" borderId="294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="419" fillId="0" borderId="295" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="420" fillId="0" borderId="296" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="421" fillId="0" borderId="297" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="422" fillId="0" borderId="298" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="423" fillId="0" borderId="299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="424" fillId="0" borderId="300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="425" fillId="0" borderId="301" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="426" fillId="0" borderId="302" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="427" fillId="0" borderId="303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="428" fillId="0" borderId="304" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="430" fillId="0" borderId="305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="432" fillId="0" borderId="306" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="434" fillId="0" borderId="307" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="436" fillId="0" borderId="308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="438" fillId="0" borderId="309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="440" fillId="0" borderId="310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="442" fillId="0" borderId="311" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="444" fillId="0" borderId="312" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="446" fillId="0" borderId="313" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="448" fillId="0" borderId="314" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="450" fillId="0" borderId="315" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="452" fillId="0" borderId="316" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4058,111 +5373,111 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="160" customWidth="true"/>
-    <col min="2" max="2" width="12.7109375" style="161" customWidth="true"/>
-    <col min="3" max="5" width="15.7109375" style="162" customWidth="true"/>
+    <col min="1" max="1" width="2.7109375" style="239" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" style="240" customWidth="true"/>
+    <col min="3" max="5" width="15.7109375" style="241" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="159" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="183" t="s">
+    <row r="1" s="238" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="262" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="183" t="s">
+      <c r="B1" s="262" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="183" t="s">
+      <c r="C1" s="262" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="183" t="s">
+      <c r="D1" s="262" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="183" t="s">
+      <c r="E1" s="262" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="160" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="212" t="s">
+      <c r="B2" s="291" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="205" t="s">
+      <c r="C2" s="284" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="285" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="217" t="s">
+      <c r="E2" s="296" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="160" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="213" t="s">
+      <c r="B3" s="292" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="209" t="s">
+      <c r="C3" s="288" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="210" t="s">
+      <c r="D3" s="289" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="218" t="s">
+      <c r="E3" s="297" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="81" t="s">
+      <c r="A4" s="160" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="226" t="s">
+      <c r="B4" s="305" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="227" t="s">
-        <v>7</v>
+      <c r="C4" s="306">
+        <v>6072.4230769230771</v>
       </c>
-      <c r="D4" s="228" t="s">
-        <v>11</v>
+      <c r="D4" s="307">
+        <v>19.82692307692308</v>
       </c>
-      <c r="E4" s="229" t="s">
-        <v>15</v>
+      <c r="E4" s="308">
+        <v>3317.1153846153852</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="160" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="230" t="s">
+      <c r="B5" s="309" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="231" t="s">
-        <v>8</v>
+      <c r="C5" s="310">
+        <v>6384.681818181818</v>
       </c>
-      <c r="D5" s="232" t="s">
-        <v>12</v>
+      <c r="D5" s="311">
+        <v>24.77272727272727</v>
       </c>
-      <c r="E5" s="233" t="s">
-        <v>16</v>
+      <c r="E5" s="312">
+        <v>2315.909090909091</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="81" t="s">
+      <c r="A6" s="160" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="234" t="s">
+      <c r="B6" s="313" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="235" t="s">
-        <v>9</v>
+      <c r="C6" s="314">
+        <v>6165.2567567567567</v>
       </c>
-      <c r="D6" s="236" t="s">
-        <v>13</v>
+      <c r="D6" s="315">
+        <v>21.297297297297298</v>
       </c>
-      <c r="E6" s="237" t="s">
-        <v>17</v>
+      <c r="E6" s="316">
+        <v>3019.45945945946</v>
       </c>
     </row>
   </sheetData>

--- a/tabtools/demo/tablex.xlsx
+++ b/tabtools/demo/tablex.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="120" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="150" uniqueCount="18">
   <si>
     <t>Table 4. Summary by Origin</t>
   </si>
@@ -73,10 +73,492 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="453">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="566">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2015,7 +2497,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="317">
+  <borders count="396">
     <border>
       <left/>
       <right/>
@@ -4139,11 +4621,540 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="317">
+  <cellXfs count="396">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -5358,6 +6369,310 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="452" fillId="0" borderId="316" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="317" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="318" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="319" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="320" xfId="0"/>
+    <xf numFmtId="0" fontId="453" fillId="0" borderId="321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="454" fillId="0" borderId="322" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="455" fillId="0" borderId="323" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="456" fillId="0" borderId="324" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="457" fillId="0" borderId="325" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="458" fillId="0" borderId="326" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="459" fillId="0" borderId="327" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="460" fillId="0" borderId="328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="461" fillId="0" borderId="329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="462" fillId="0" borderId="330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="464" fillId="0" borderId="331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="466" fillId="0" borderId="332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="468" fillId="0" borderId="333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="470" fillId="0" borderId="334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="472" fillId="0" borderId="335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="474" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="476" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="478" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="480" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="482" fillId="0" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="483" fillId="0" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="484" fillId="0" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="485" fillId="0" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="486" fillId="0" borderId="344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="487" fillId="0" borderId="345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="489" fillId="0" borderId="346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="491" fillId="0" borderId="347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="493" fillId="0" borderId="348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="495" fillId="0" borderId="349" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="497" fillId="0" borderId="350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="499" fillId="0" borderId="351" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="501" fillId="0" borderId="352" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="503" fillId="0" borderId="353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="505" fillId="0" borderId="354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="507" fillId="0" borderId="355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="509" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="511" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="513" fillId="0" borderId="358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="515" fillId="0" borderId="359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="517" fillId="0" borderId="360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="519" fillId="0" borderId="361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="520" fillId="0" borderId="362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="521" fillId="0" borderId="363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="522" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="523" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="524" fillId="0" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="525" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="526" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="527" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="528" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="529" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="530" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="531" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="532" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="533" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="534" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="535" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="536" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="537" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="538" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="539" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="540" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="541" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="543" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="545" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="547" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="549" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="551" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="553" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="555" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="557" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="559" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="561" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="563" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="565" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5373,110 +6688,110 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="239" customWidth="true"/>
-    <col min="2" max="2" width="12.7109375" style="240" customWidth="true"/>
-    <col min="3" max="5" width="15.7109375" style="241" customWidth="true"/>
+    <col min="1" max="1" width="2.7109375" style="318" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" style="319" customWidth="true"/>
+    <col min="3" max="5" width="15.7109375" style="320" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="238" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="262" t="s">
+    <row r="1" s="317" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="341" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="262" t="s">
+      <c r="B1" s="341" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="262" t="s">
+      <c r="C1" s="341" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="262" t="s">
+      <c r="D1" s="341" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="262" t="s">
+      <c r="E1" s="341" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="160" t="s">
+      <c r="A2" s="239" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="291" t="s">
+      <c r="B2" s="370" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="284" t="s">
+      <c r="C2" s="363" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="285" t="s">
+      <c r="D2" s="364" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="296" t="s">
+      <c r="E2" s="375" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="160" t="s">
+      <c r="A3" s="239" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="292" t="s">
+      <c r="B3" s="371" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="288" t="s">
+      <c r="C3" s="367" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="289" t="s">
+      <c r="D3" s="368" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="297" t="s">
+      <c r="E3" s="376" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="160" t="s">
+      <c r="A4" s="239" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="305" t="s">
+      <c r="B4" s="384" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="306">
+      <c r="C4" s="385">
         <v>6072.4230769230771</v>
       </c>
-      <c r="D4" s="307">
+      <c r="D4" s="386">
         <v>19.82692307692308</v>
       </c>
-      <c r="E4" s="308">
+      <c r="E4" s="387">
         <v>3317.1153846153852</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="160" t="s">
+      <c r="A5" s="239" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="309" t="s">
+      <c r="B5" s="388" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="310">
+      <c r="C5" s="389">
         <v>6384.681818181818</v>
       </c>
-      <c r="D5" s="311">
+      <c r="D5" s="390">
         <v>24.77272727272727</v>
       </c>
-      <c r="E5" s="312">
+      <c r="E5" s="391">
         <v>2315.909090909091</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="160" t="s">
+      <c r="A6" s="239" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="313" t="s">
+      <c r="B6" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="314">
+      <c r="C6" s="393">
         <v>6165.2567567567567</v>
       </c>
-      <c r="D6" s="315">
+      <c r="D6" s="394">
         <v>21.297297297297298</v>
       </c>
-      <c r="E6" s="316">
+      <c r="E6" s="395">
         <v>3019.45945945946</v>
       </c>
     </row>
